--- a/tests/files/test.xlsx
+++ b/tests/files/test.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29127"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29426"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\WWW\domains\dev.loc\fast-excel-templator\tests\files\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{44D54E38-A9FF-4573-A440-D9B09083C4E2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E19179E8-CB79-40A4-9ED9-3E5C0D4E8E70}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="43080" yWindow="-120" windowWidth="29040" windowHeight="17520" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="47025" yWindow="2910" windowWidth="16200" windowHeight="9315" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -35,15 +35,27 @@
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="2">
+  <fills count="4">
     <fill>
       <patternFill patternType="none"/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFF00"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.79998168889431442"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
   </fills>
-  <borders count="1">
+  <borders count="5">
     <border>
       <left/>
       <right/>
@@ -51,15 +63,81 @@
       <bottom/>
       <diagonal/>
     </border>
+    <border>
+      <left style="medium">
+        <color indexed="64"/>
+      </left>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top style="medium">
+        <color indexed="64"/>
+      </top>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right style="medium">
+        <color indexed="64"/>
+      </right>
+      <top style="medium">
+        <color indexed="64"/>
+      </top>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="medium">
+        <color indexed="64"/>
+      </left>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom style="medium">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right style="medium">
+        <color indexed="64"/>
+      </right>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom style="medium">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="1">
+  <cellXfs count="7">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="1">
-    <cellStyle name="Обычный" xfId="0" builtinId="0"/>
+    <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
   <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
@@ -337,13 +415,26 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1"/>
+  <dimension ref="A1:D5"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
+  <cols>
+    <col min="2" max="2" width="9.06640625" style="1"/>
+  </cols>
   <sheetData>
-    <row r="1" spans="1:1" x14ac:dyDescent="0.45">
+    <row r="1" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A1">
         <v>1</v>
       </c>
+    </row>
+    <row r="2" spans="1:4" s="2" customFormat="1" x14ac:dyDescent="0.45"/>
+    <row r="3" spans="1:4" ht="14.65" thickBot="1" x14ac:dyDescent="0.5"/>
+    <row r="4" spans="1:4" x14ac:dyDescent="0.45">
+      <c r="C4" s="3"/>
+      <c r="D4" s="4"/>
+    </row>
+    <row r="5" spans="1:4" ht="14.65" thickBot="1" x14ac:dyDescent="0.5">
+      <c r="C5" s="5"/>
+      <c r="D5" s="6"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
